--- a/Result/profitability/4106.xlsx
+++ b/Result/profitability/4106.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.43</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3275</v>
+        <v>0.39625</v>
       </c>
       <c r="N2" t="n">
-        <v>43.95</v>
+        <v>44.71</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.67</v>
       </c>
       <c r="M3" t="n">
-        <v>0.40125</v>
+        <v>0.4225</v>
       </c>
       <c r="N3" t="n">
-        <v>43.95</v>
+        <v>44.38</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.71</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4325</v>
+        <v>0.4825</v>
       </c>
       <c r="N4" t="n">
-        <v>43.125</v>
+        <v>43.40125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.53</v>
       </c>
       <c r="M5" t="n">
-        <v>0.47</v>
+        <v>0.52125</v>
       </c>
       <c r="N5" t="n">
-        <v>41.28</v>
+        <v>41.8325</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.66</v>
       </c>
       <c r="M6" t="n">
-        <v>0.525</v>
+        <v>0.54625</v>
       </c>
       <c r="N6" t="n">
-        <v>40.46</v>
+        <v>40.78875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.85</v>
       </c>
       <c r="M7" t="n">
-        <v>0.57375</v>
+        <v>0.6174999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>39.32875</v>
+        <v>39.87625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.61</v>
       </c>
       <c r="M8" t="n">
-        <v>0.615</v>
+        <v>0.63625</v>
       </c>
       <c r="N8" t="n">
-        <v>38.22375</v>
+        <v>38.20875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.665</v>
       </c>
       <c r="N9" t="n">
-        <v>36.9825</v>
+        <v>36.98249999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.67625</v>
       </c>
       <c r="N13" t="n">
-        <v>37.9825</v>
+        <v>37.98249999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>674</v>
+      </c>
+      <c r="D75" t="n">
+        <v>341</v>
+      </c>
+      <c r="E75" t="n">
+        <v>333</v>
+      </c>
+      <c r="F75" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>75</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.16%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>76</v>
+      </c>
+      <c r="K75" t="n">
+        <v>64</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="N75" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3695652173913042</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1199999999999974</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.002426202992316995</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.863636363636364</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.420000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09839715048975961</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
